--- a/templates/ERC000041/metadata_template_ERC000041.xlsx
+++ b/templates/ERC000041/metadata_template_ERC000041.xlsx
@@ -19,7 +19,7 @@
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
     <definedName name="geographiclocationcountryandorsea">'cv_sample'!$S$1:$S$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$85</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="611" uniqueCount="603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="605">
   <si>
     <t>alias</t>
   </si>
@@ -555,6 +555,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -718,6 +721,9 @@
   </si>
   <si>
     <t>UG 100</t>
+  </si>
+  <si>
+    <t>Vega</t>
   </si>
   <si>
     <t>instrument_model</t>
@@ -2369,7 +2375,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2413,7 +2419,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2440,7 +2446,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N85"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3159,6 +3165,16 @@
     </row>
     <row r="85" spans="14:14">
       <c r="N85" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="14:14">
+      <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3180,27 +3196,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3220,122 +3236,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3359,162 +3375,162 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
     </row>
   </sheetData>
@@ -3534,1447 +3550,1447 @@
   <sheetData>
     <row r="1" spans="19:19">
       <c r="S1" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="19:19">
       <c r="S2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="19:19">
       <c r="S3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="19:19">
       <c r="S4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="19:19">
       <c r="S5" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="19:19">
       <c r="S6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="19:19">
       <c r="S7" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="19:19">
       <c r="S8" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="19:19">
       <c r="S9" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="19:19">
       <c r="S10" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="19:19">
       <c r="S11" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="19:19">
       <c r="S12" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="19:19">
       <c r="S13" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="19:19">
       <c r="S14" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="19:19">
       <c r="S15" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="19:19">
       <c r="S16" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="19:19">
       <c r="S17" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="19:19">
       <c r="S18" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="19:19">
       <c r="S19" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" spans="19:19">
       <c r="S20" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="19:19">
       <c r="S21" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" spans="19:19">
       <c r="S22" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="19:19">
       <c r="S23" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24" spans="19:19">
       <c r="S24" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="19:19">
       <c r="S25" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="19:19">
       <c r="S26" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" spans="19:19">
       <c r="S27" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="19:19">
       <c r="S28" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="19:19">
       <c r="S29" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" spans="19:19">
       <c r="S30" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="31" spans="19:19">
       <c r="S31" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="32" spans="19:19">
       <c r="S32" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" spans="19:19">
       <c r="S33" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="34" spans="19:19">
       <c r="S34" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="35" spans="19:19">
       <c r="S35" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36" spans="19:19">
       <c r="S36" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="37" spans="19:19">
       <c r="S37" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38" spans="19:19">
       <c r="S38" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="39" spans="19:19">
       <c r="S39" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="19:19">
       <c r="S40" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="41" spans="19:19">
       <c r="S41" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="42" spans="19:19">
       <c r="S42" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="19:19">
       <c r="S43" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="19:19">
       <c r="S44" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="45" spans="19:19">
       <c r="S45" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="46" spans="19:19">
       <c r="S46" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="47" spans="19:19">
       <c r="S47" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="48" spans="19:19">
       <c r="S48" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="49" spans="19:19">
       <c r="S49" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="50" spans="19:19">
       <c r="S50" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="51" spans="19:19">
       <c r="S51" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="52" spans="19:19">
       <c r="S52" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="53" spans="19:19">
       <c r="S53" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="54" spans="19:19">
       <c r="S54" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="55" spans="19:19">
       <c r="S55" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="56" spans="19:19">
       <c r="S56" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="57" spans="19:19">
       <c r="S57" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="58" spans="19:19">
       <c r="S58" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="59" spans="19:19">
       <c r="S59" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="60" spans="19:19">
       <c r="S60" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="61" spans="19:19">
       <c r="S61" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="62" spans="19:19">
       <c r="S62" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="63" spans="19:19">
       <c r="S63" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="64" spans="19:19">
       <c r="S64" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="65" spans="19:19">
       <c r="S65" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="66" spans="19:19">
       <c r="S66" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="67" spans="19:19">
       <c r="S67" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="68" spans="19:19">
       <c r="S68" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="69" spans="19:19">
       <c r="S69" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="70" spans="19:19">
       <c r="S70" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="71" spans="19:19">
       <c r="S71" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="72" spans="19:19">
       <c r="S72" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="73" spans="19:19">
       <c r="S73" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="74" spans="19:19">
       <c r="S74" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="75" spans="19:19">
       <c r="S75" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="76" spans="19:19">
       <c r="S76" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="77" spans="19:19">
       <c r="S77" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="78" spans="19:19">
       <c r="S78" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="79" spans="19:19">
       <c r="S79" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="80" spans="19:19">
       <c r="S80" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="81" spans="19:19">
       <c r="S81" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="82" spans="19:19">
       <c r="S82" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="83" spans="19:19">
       <c r="S83" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="84" spans="19:19">
       <c r="S84" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="85" spans="19:19">
       <c r="S85" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="86" spans="19:19">
       <c r="S86" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="87" spans="19:19">
       <c r="S87" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="88" spans="19:19">
       <c r="S88" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="89" spans="19:19">
       <c r="S89" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="90" spans="19:19">
       <c r="S90" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="91" spans="19:19">
       <c r="S91" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="92" spans="19:19">
       <c r="S92" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="93" spans="19:19">
       <c r="S93" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="94" spans="19:19">
       <c r="S94" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="95" spans="19:19">
       <c r="S95" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="96" spans="19:19">
       <c r="S96" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="97" spans="19:19">
       <c r="S97" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="98" spans="19:19">
       <c r="S98" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="99" spans="19:19">
       <c r="S99" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="100" spans="19:19">
       <c r="S100" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="101" spans="19:19">
       <c r="S101" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="102" spans="19:19">
       <c r="S102" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="103" spans="19:19">
       <c r="S103" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="104" spans="19:19">
       <c r="S104" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="105" spans="19:19">
       <c r="S105" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="106" spans="19:19">
       <c r="S106" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="107" spans="19:19">
       <c r="S107" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="108" spans="19:19">
       <c r="S108" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="109" spans="19:19">
       <c r="S109" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="110" spans="19:19">
       <c r="S110" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="111" spans="19:19">
       <c r="S111" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="112" spans="19:19">
       <c r="S112" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="113" spans="19:19">
       <c r="S113" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="114" spans="19:19">
       <c r="S114" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="115" spans="19:19">
       <c r="S115" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="116" spans="19:19">
       <c r="S116" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="117" spans="19:19">
       <c r="S117" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="118" spans="19:19">
       <c r="S118" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="119" spans="19:19">
       <c r="S119" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="120" spans="19:19">
       <c r="S120" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="121" spans="19:19">
       <c r="S121" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="122" spans="19:19">
       <c r="S122" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="123" spans="19:19">
       <c r="S123" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="124" spans="19:19">
       <c r="S124" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="125" spans="19:19">
       <c r="S125" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="126" spans="19:19">
       <c r="S126" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="127" spans="19:19">
       <c r="S127" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="128" spans="19:19">
       <c r="S128" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="129" spans="19:19">
       <c r="S129" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="130" spans="19:19">
       <c r="S130" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="131" spans="19:19">
       <c r="S131" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="132" spans="19:19">
       <c r="S132" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="133" spans="19:19">
       <c r="S133" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="134" spans="19:19">
       <c r="S134" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="135" spans="19:19">
       <c r="S135" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="136" spans="19:19">
       <c r="S136" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="137" spans="19:19">
       <c r="S137" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="138" spans="19:19">
       <c r="S138" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="139" spans="19:19">
       <c r="S139" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="140" spans="19:19">
       <c r="S140" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="141" spans="19:19">
       <c r="S141" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="142" spans="19:19">
       <c r="S142" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="143" spans="19:19">
       <c r="S143" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="144" spans="19:19">
       <c r="S144" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="145" spans="19:19">
       <c r="S145" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="146" spans="19:19">
       <c r="S146" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="147" spans="19:19">
       <c r="S147" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="148" spans="19:19">
       <c r="S148" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="149" spans="19:19">
       <c r="S149" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="150" spans="19:19">
       <c r="S150" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="151" spans="19:19">
       <c r="S151" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="152" spans="19:19">
       <c r="S152" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="153" spans="19:19">
       <c r="S153" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="154" spans="19:19">
       <c r="S154" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="155" spans="19:19">
       <c r="S155" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="156" spans="19:19">
       <c r="S156" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="157" spans="19:19">
       <c r="S157" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="158" spans="19:19">
       <c r="S158" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="159" spans="19:19">
       <c r="S159" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="160" spans="19:19">
       <c r="S160" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="161" spans="19:19">
       <c r="S161" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="162" spans="19:19">
       <c r="S162" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="163" spans="19:19">
       <c r="S163" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="164" spans="19:19">
       <c r="S164" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="165" spans="19:19">
       <c r="S165" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="166" spans="19:19">
       <c r="S166" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="167" spans="19:19">
       <c r="S167" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="168" spans="19:19">
       <c r="S168" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="169" spans="19:19">
       <c r="S169" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="170" spans="19:19">
       <c r="S170" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="171" spans="19:19">
       <c r="S171" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="172" spans="19:19">
       <c r="S172" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="173" spans="19:19">
       <c r="S173" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="174" spans="19:19">
       <c r="S174" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="175" spans="19:19">
       <c r="S175" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="176" spans="19:19">
       <c r="S176" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="177" spans="19:19">
       <c r="S177" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="178" spans="19:19">
       <c r="S178" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="179" spans="19:19">
       <c r="S179" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="180" spans="19:19">
       <c r="S180" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="181" spans="19:19">
       <c r="S181" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="182" spans="19:19">
       <c r="S182" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="183" spans="19:19">
       <c r="S183" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="184" spans="19:19">
       <c r="S184" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="185" spans="19:19">
       <c r="S185" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="186" spans="19:19">
       <c r="S186" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="187" spans="19:19">
       <c r="S187" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="188" spans="19:19">
       <c r="S188" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="189" spans="19:19">
       <c r="S189" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="190" spans="19:19">
       <c r="S190" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="191" spans="19:19">
       <c r="S191" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="192" spans="19:19">
       <c r="S192" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="193" spans="19:19">
       <c r="S193" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="194" spans="19:19">
       <c r="S194" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="195" spans="19:19">
       <c r="S195" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="196" spans="19:19">
       <c r="S196" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="197" spans="19:19">
       <c r="S197" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="198" spans="19:19">
       <c r="S198" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="199" spans="19:19">
       <c r="S199" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="200" spans="19:19">
       <c r="S200" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="201" spans="19:19">
       <c r="S201" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="202" spans="19:19">
       <c r="S202" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="203" spans="19:19">
       <c r="S203" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="204" spans="19:19">
       <c r="S204" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="205" spans="19:19">
       <c r="S205" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="206" spans="19:19">
       <c r="S206" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="207" spans="19:19">
       <c r="S207" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="208" spans="19:19">
       <c r="S208" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="209" spans="19:19">
       <c r="S209" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="210" spans="19:19">
       <c r="S210" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="211" spans="19:19">
       <c r="S211" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="212" spans="19:19">
       <c r="S212" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="213" spans="19:19">
       <c r="S213" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="19:19">
       <c r="S214" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="215" spans="19:19">
       <c r="S215" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="216" spans="19:19">
       <c r="S216" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="217" spans="19:19">
       <c r="S217" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="218" spans="19:19">
       <c r="S218" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="219" spans="19:19">
       <c r="S219" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="220" spans="19:19">
       <c r="S220" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="221" spans="19:19">
       <c r="S221" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="222" spans="19:19">
       <c r="S222" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="223" spans="19:19">
       <c r="S223" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="224" spans="19:19">
       <c r="S224" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="225" spans="19:19">
       <c r="S225" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="226" spans="19:19">
       <c r="S226" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
     </row>
     <row r="227" spans="19:19">
       <c r="S227" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="228" spans="19:19">
       <c r="S228" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="229" spans="19:19">
       <c r="S229" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="230" spans="19:19">
       <c r="S230" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="231" spans="19:19">
       <c r="S231" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
     </row>
     <row r="232" spans="19:19">
       <c r="S232" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
     </row>
     <row r="233" spans="19:19">
       <c r="S233" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
     </row>
     <row r="234" spans="19:19">
       <c r="S234" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
     </row>
     <row r="235" spans="19:19">
       <c r="S235" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
     </row>
     <row r="236" spans="19:19">
       <c r="S236" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
     </row>
     <row r="237" spans="19:19">
       <c r="S237" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
     </row>
     <row r="238" spans="19:19">
       <c r="S238" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="239" spans="19:19">
       <c r="S239" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
     </row>
     <row r="240" spans="19:19">
       <c r="S240" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
     </row>
     <row r="241" spans="19:19">
       <c r="S241" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
     </row>
     <row r="242" spans="19:19">
       <c r="S242" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
     </row>
     <row r="243" spans="19:19">
       <c r="S243" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
     </row>
     <row r="244" spans="19:19">
       <c r="S244" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
     </row>
     <row r="245" spans="19:19">
       <c r="S245" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
     </row>
     <row r="246" spans="19:19">
       <c r="S246" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="247" spans="19:19">
       <c r="S247" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
     </row>
     <row r="248" spans="19:19">
       <c r="S248" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
     </row>
     <row r="249" spans="19:19">
       <c r="S249" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
     </row>
     <row r="250" spans="19:19">
       <c r="S250" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
     </row>
     <row r="251" spans="19:19">
       <c r="S251" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
     </row>
     <row r="252" spans="19:19">
       <c r="S252" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
     </row>
     <row r="253" spans="19:19">
       <c r="S253" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
     </row>
     <row r="254" spans="19:19">
       <c r="S254" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="255" spans="19:19">
       <c r="S255" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="256" spans="19:19">
       <c r="S256" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="257" spans="19:19">
       <c r="S257" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
     </row>
     <row r="258" spans="19:19">
       <c r="S258" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="259" spans="19:19">
       <c r="S259" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
     </row>
     <row r="260" spans="19:19">
       <c r="S260" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
     </row>
     <row r="261" spans="19:19">
       <c r="S261" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
     </row>
     <row r="262" spans="19:19">
       <c r="S262" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
     </row>
     <row r="263" spans="19:19">
       <c r="S263" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="264" spans="19:19">
       <c r="S264" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
     </row>
     <row r="265" spans="19:19">
       <c r="S265" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="266" spans="19:19">
       <c r="S266" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="267" spans="19:19">
       <c r="S267" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="268" spans="19:19">
       <c r="S268" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="269" spans="19:19">
       <c r="S269" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
     </row>
     <row r="270" spans="19:19">
       <c r="S270" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
     </row>
     <row r="271" spans="19:19">
       <c r="S271" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
     </row>
     <row r="272" spans="19:19">
       <c r="S272" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="273" spans="19:19">
       <c r="S273" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
     </row>
     <row r="274" spans="19:19">
       <c r="S274" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="275" spans="19:19">
       <c r="S275" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
     </row>
     <row r="276" spans="19:19">
       <c r="S276" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
     </row>
     <row r="277" spans="19:19">
       <c r="S277" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
     </row>
     <row r="278" spans="19:19">
       <c r="S278" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
     </row>
     <row r="279" spans="19:19">
       <c r="S279" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="280" spans="19:19">
       <c r="S280" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="281" spans="19:19">
       <c r="S281" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="282" spans="19:19">
       <c r="S282" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
     </row>
     <row r="283" spans="19:19">
       <c r="S283" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
     </row>
     <row r="284" spans="19:19">
       <c r="S284" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
     </row>
     <row r="285" spans="19:19">
       <c r="S285" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
     </row>
     <row r="286" spans="19:19">
       <c r="S286" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
     </row>
     <row r="287" spans="19:19">
       <c r="S287" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
     </row>
     <row r="288" spans="19:19">
       <c r="S288" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
     </row>
     <row r="289" spans="19:19">
       <c r="S289" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000041/metadata_template_ERC000041.xlsx
+++ b/templates/ERC000041/metadata_template_ERC000041.xlsx
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="fileformat">'cv_run'!$D$1:$D$24</definedName>
-    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$S$1:$S$289</definedName>
-    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$86</definedName>
+    <definedName name="geographiclocationcountryandorsea">'cv_sample'!$S$1:$S$294</definedName>
+    <definedName name="instrumentmodel">'cv_experiment'!$N$1:$N$87</definedName>
     <definedName name="libraryselection">'cv_experiment'!$I$1:$I$31</definedName>
     <definedName name="librarysource">'cv_experiment'!$H$1:$H$9</definedName>
     <definedName name="librarystrategy">'cv_experiment'!$G$1:$G$41</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="610">
   <si>
     <t>alias</t>
   </si>
@@ -555,6 +555,9 @@
     <t>DNBSEQ-G50</t>
   </si>
   <si>
+    <t>DNBSEQ-G800</t>
+  </si>
+  <si>
     <t>DNBSEQ-T10x4RS</t>
   </si>
   <si>
@@ -840,49 +843,49 @@
     <t>(Optional) Free-form text describing the sample, its origin, and its method of isolation.</t>
   </si>
   <si>
-    <t>sample transportation date</t>
+    <t>sample_transportation_date</t>
   </si>
   <si>
     <t>(Optional) Transportation/shipping date of the sample. format:yyyy-mm-dd</t>
   </si>
   <si>
-    <t>sample transportation temperature</t>
+    <t>sample_transportation_temperature</t>
   </si>
   <si>
     <t>(Optional) Temperature at which sample was transported, e.g. -20 or 4 degree celsius. (Units: °C)</t>
   </si>
   <si>
-    <t>sample transportation time</t>
+    <t>sample_transportation_time</t>
   </si>
   <si>
     <t>(Optional) Transportation time from sample site to storage</t>
   </si>
   <si>
-    <t>sample storage temperature</t>
+    <t>sample_storage_temperature</t>
   </si>
   <si>
     <t>(Optional) Temperature at which sample was stored, e.g. -80 (Units: °C)</t>
   </si>
   <si>
-    <t>sample storage location</t>
+    <t>sample_storage_location</t>
   </si>
   <si>
     <t>(Optional) Location at which sample was stored, usually name of a specific freezer/room. indicate the location name.</t>
   </si>
   <si>
-    <t>instrument for DNA concentration measurement</t>
+    <t>instrument_for_dna_concentration_measurement</t>
   </si>
   <si>
     <t>(Optional) Name/type of instrument used to measure the dna concentration (ng/µl) prior to library preparation</t>
   </si>
   <si>
-    <t>read quality filter</t>
+    <t>read_quality_filter</t>
   </si>
   <si>
     <t>(Optional) Programme used to filter reads quality before conducting the analysis</t>
   </si>
   <si>
-    <t>DNA concentration</t>
+    <t>dna_concentration</t>
   </si>
   <si>
     <t>(Optional) Dna concentration used for sequencing in ng/µl (Units: ng/µl)</t>
@@ -894,31 +897,31 @@
     <t>(Optional) Describes the physical, environmental and/or local geographical source of the biological sample from which the sample was derived</t>
   </si>
   <si>
-    <t>collection date</t>
+    <t>collection_date</t>
   </si>
   <si>
     <t>(Mandatory) The date the sample was collected with the intention of sequencing, either as an instance (single point in time) or interval. in case no exact time is available, the date/time can be right truncated i.e. all of these are valid iso8601 compliant times: 2008-01-23t19:23:10+00:00; 2008-01-23t19:23:10; 2008-01-23; 2008-01; 2008.</t>
   </si>
   <si>
-    <t>geographic location (region and locality)</t>
+    <t>geographic_location_region_and_locality</t>
   </si>
   <si>
     <t>(Recommended) The geographical origin of the sample as defined by the specific region name followed by the locality name.</t>
   </si>
   <si>
-    <t>amount or size of sample collected</t>
-  </si>
-  <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
-  </si>
-  <si>
-    <t>sampling time point</t>
+    <t>amount_or_size_of_sample_collected</t>
+  </si>
+  <si>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
+  </si>
+  <si>
+    <t>sampling_time_point</t>
   </si>
   <si>
     <t>(Optional) Time point at which a sample or observation is made or taken from a biomaterial as measured from some reference point. indicate the timepoint written in iso 8601 format.</t>
   </si>
   <si>
-    <t>sample storage duration</t>
+    <t>sample_storage_duration</t>
   </si>
   <si>
     <t>(Optional) Duration for which the sample was stored. indicate the duration for which the sample was stored written in iso 8601 format.</t>
@@ -1137,9 +1140,6 @@
     <t>Dominican Republic</t>
   </si>
   <si>
-    <t>East Timor</t>
-  </si>
-  <si>
     <t>Ecuador</t>
   </si>
   <si>
@@ -1158,6 +1158,9 @@
     <t>Estonia</t>
   </si>
   <si>
+    <t>Eswatini</t>
+  </si>
+  <si>
     <t>Ethiopia</t>
   </si>
   <si>
@@ -1359,6 +1362,9 @@
     <t>Liechtenstein</t>
   </si>
   <si>
+    <t>Line Islands</t>
+  </si>
+  <si>
     <t>Lithuania</t>
   </si>
   <si>
@@ -1368,9 +1374,6 @@
     <t>Macau</t>
   </si>
   <si>
-    <t>Macedonia</t>
-  </si>
-  <si>
     <t>Madagascar</t>
   </si>
   <si>
@@ -1410,7 +1413,7 @@
     <t>Mexico</t>
   </si>
   <si>
-    <t>Micronesia</t>
+    <t>Micronesia, Federated States of</t>
   </si>
   <si>
     <t>Midway Islands</t>
@@ -1479,6 +1482,9 @@
     <t>North Korea</t>
   </si>
   <si>
+    <t>North Macedonia</t>
+  </si>
+  <si>
     <t>North Sea</t>
   </si>
   <si>
@@ -1554,6 +1560,9 @@
     <t>Rwanda</t>
   </si>
   <si>
+    <t>Saint Barthelemy</t>
+  </si>
+  <si>
     <t>Saint Helena</t>
   </si>
   <si>
@@ -1575,6 +1584,9 @@
     <t>San Marino</t>
   </si>
   <si>
+    <t>Saint Martin</t>
+  </si>
+  <si>
     <t>Sao Tome and Principe</t>
   </si>
   <si>
@@ -1620,6 +1632,9 @@
     <t>South Korea</t>
   </si>
   <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
     <t>Southern Ocean</t>
   </si>
   <si>
@@ -1632,6 +1647,9 @@
     <t>Sri Lanka</t>
   </si>
   <si>
+    <t>State of Palestine</t>
+  </si>
+  <si>
     <t>Sudan</t>
   </si>
   <si>
@@ -1641,9 +1659,6 @@
     <t>Svalbard</t>
   </si>
   <si>
-    <t>Swaziland</t>
-  </si>
-  <si>
     <t>Sweden</t>
   </si>
   <si>
@@ -1668,6 +1683,9 @@
     <t>Thailand</t>
   </si>
   <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
     <t>Togo</t>
   </si>
   <si>
@@ -1728,12 +1746,12 @@
     <t>Viet Nam</t>
   </si>
   <si>
+    <t>Wake Island</t>
+  </si>
+  <si>
     <t>Virgin Islands</t>
   </si>
   <si>
-    <t>Wake Island</t>
-  </si>
-  <si>
     <t>Wallis and Futuna</t>
   </si>
   <si>
@@ -1791,19 +1809,19 @@
     <t>restricted access</t>
   </si>
   <si>
-    <t>geographic location (country and/or sea)</t>
+    <t>geographic_location_country_andor_sea</t>
   </si>
   <si>
     <t>(Mandatory) The geographical origin of where the sample was collected from, with the intention of sequencing, as defined by the country or sea name. country or sea names should be chosen from the insdc country list (http://insdc.org/country.html).</t>
   </si>
   <si>
-    <t>receipt date</t>
+    <t>receipt_date</t>
   </si>
   <si>
     <t>(Recommended) Date on which the sample was received. format:yyyy-mm-dd. please provide the highest precision possible. if the sample was received by the institution and not collected, the 'receipt date' must be provided instead. either the 'collection date' or 'receipt date' must be provided. if available, provide both dates.</t>
   </si>
   <si>
-    <t>links to additional analysis</t>
+    <t>links_to_additional_analysis</t>
   </si>
   <si>
     <t>(Recommended) Link to additional analysis results performed on the sample</t>
@@ -1821,19 +1839,19 @@
     <t>(Recommended) Name of sub-species of organism from which sample was obtained</t>
   </si>
   <si>
-    <t>Further Details</t>
+    <t>further_details</t>
   </si>
   <si>
     <t>(Recommended) Reference details related to a sample in form of an uri.</t>
   </si>
   <si>
-    <t>nucleic acid extraction</t>
+    <t>nucleic_acid_extraction</t>
   </si>
   <si>
     <t>(Optional) A link to a literature reference, electronic resource or a standard operating procedure (sop), that describes the material separation to recover the nucleic acid fraction from a sample</t>
   </si>
   <si>
-    <t>library construction method</t>
+    <t>library_construction_method</t>
   </si>
   <si>
     <t>(Optional) Library construction method used for clone libraries</t>
@@ -2372,7 +2390,7 @@
         <v>143</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="150" customHeight="1">
@@ -2416,7 +2434,7 @@
         <v>144</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -2443,7 +2461,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="G1:N86"/>
+  <dimension ref="G1:N87"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="7:14">
@@ -3167,6 +3185,11 @@
     </row>
     <row r="86" spans="14:14">
       <c r="N86" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="87" spans="14:14">
+      <c r="N87" t="s">
         <v>117</v>
       </c>
     </row>
@@ -3188,27 +3211,27 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
   </sheetData>
@@ -3228,122 +3251,122 @@
   <sheetData>
     <row r="1" spans="4:4">
       <c r="D1" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="4:4">
       <c r="D2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="4:4">
       <c r="D3" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4" spans="4:4">
       <c r="D4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" spans="4:4">
       <c r="D5" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="6" spans="4:4">
       <c r="D6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="7" spans="4:4">
       <c r="D7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="8" spans="4:4">
       <c r="D8" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" spans="4:4">
       <c r="D9" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="4:4">
       <c r="D10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="11" spans="4:4">
       <c r="D11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="4:4">
       <c r="D12" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" spans="4:4">
       <c r="D15" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="16" spans="4:4">
       <c r="D16" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" spans="4:4">
       <c r="D17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="20" spans="4:4">
       <c r="D20" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" spans="4:4">
       <c r="D21" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="22" spans="4:4">
       <c r="D22" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="23" spans="4:4">
       <c r="D23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="24" spans="4:4">
       <c r="D24" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
   </sheetData>
@@ -3367,162 +3390,162 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>586</v>
+        <v>592</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>588</v>
+        <v>594</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>602</v>
+        <v>608</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="150" customHeight="1">
       <c r="A2" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="W2" s="2" t="s">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>599</v>
+        <v>605</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>601</v>
+        <v>607</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>603</v>
+        <v>609</v>
       </c>
     </row>
   </sheetData>
@@ -3537,1452 +3560,1477 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="S1:S289"/>
+  <dimension ref="S1:S294"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="19:19">
       <c r="S1" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="19:19">
       <c r="S2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="3" spans="19:19">
       <c r="S3" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="19:19">
       <c r="S4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="19:19">
       <c r="S5" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="6" spans="19:19">
       <c r="S6" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="19:19">
       <c r="S7" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="8" spans="19:19">
       <c r="S8" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="9" spans="19:19">
       <c r="S9" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="19:19">
       <c r="S10" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="11" spans="19:19">
       <c r="S11" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="19:19">
       <c r="S12" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="19:19">
       <c r="S13" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="14" spans="19:19">
       <c r="S14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="19:19">
       <c r="S15" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="19:19">
       <c r="S16" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="17" spans="19:19">
       <c r="S17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="18" spans="19:19">
       <c r="S18" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" spans="19:19">
       <c r="S19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="20" spans="19:19">
       <c r="S20" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="21" spans="19:19">
       <c r="S21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" spans="19:19">
       <c r="S22" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="23" spans="19:19">
       <c r="S23" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="24" spans="19:19">
       <c r="S24" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="25" spans="19:19">
       <c r="S25" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="26" spans="19:19">
       <c r="S26" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="27" spans="19:19">
       <c r="S27" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" spans="19:19">
       <c r="S28" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="29" spans="19:19">
       <c r="S29" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="30" spans="19:19">
       <c r="S30" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="31" spans="19:19">
       <c r="S31" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="32" spans="19:19">
       <c r="S32" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="33" spans="19:19">
       <c r="S33" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="34" spans="19:19">
       <c r="S34" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="35" spans="19:19">
       <c r="S35" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="36" spans="19:19">
       <c r="S36" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="37" spans="19:19">
       <c r="S37" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="38" spans="19:19">
       <c r="S38" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="39" spans="19:19">
       <c r="S39" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="40" spans="19:19">
       <c r="S40" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="41" spans="19:19">
       <c r="S41" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="42" spans="19:19">
       <c r="S42" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="43" spans="19:19">
       <c r="S43" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="44" spans="19:19">
       <c r="S44" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="45" spans="19:19">
       <c r="S45" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="46" spans="19:19">
       <c r="S46" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="47" spans="19:19">
       <c r="S47" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="48" spans="19:19">
       <c r="S48" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="49" spans="19:19">
       <c r="S49" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="50" spans="19:19">
       <c r="S50" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="51" spans="19:19">
       <c r="S51" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="52" spans="19:19">
       <c r="S52" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="53" spans="19:19">
       <c r="S53" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="54" spans="19:19">
       <c r="S54" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="55" spans="19:19">
       <c r="S55" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="56" spans="19:19">
       <c r="S56" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="57" spans="19:19">
       <c r="S57" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="58" spans="19:19">
       <c r="S58" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="59" spans="19:19">
       <c r="S59" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="60" spans="19:19">
       <c r="S60" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="61" spans="19:19">
       <c r="S61" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="62" spans="19:19">
       <c r="S62" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="63" spans="19:19">
       <c r="S63" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="64" spans="19:19">
       <c r="S64" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="65" spans="19:19">
       <c r="S65" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="66" spans="19:19">
       <c r="S66" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="67" spans="19:19">
       <c r="S67" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="68" spans="19:19">
       <c r="S68" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="69" spans="19:19">
       <c r="S69" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="70" spans="19:19">
       <c r="S70" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="71" spans="19:19">
       <c r="S71" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="72" spans="19:19">
       <c r="S72" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="73" spans="19:19">
       <c r="S73" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="74" spans="19:19">
       <c r="S74" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="75" spans="19:19">
       <c r="S75" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="76" spans="19:19">
       <c r="S76" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="77" spans="19:19">
       <c r="S77" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="78" spans="19:19">
       <c r="S78" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="79" spans="19:19">
       <c r="S79" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="80" spans="19:19">
       <c r="S80" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="81" spans="19:19">
       <c r="S81" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="82" spans="19:19">
       <c r="S82" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="83" spans="19:19">
       <c r="S83" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="84" spans="19:19">
       <c r="S84" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="85" spans="19:19">
       <c r="S85" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="86" spans="19:19">
       <c r="S86" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="87" spans="19:19">
       <c r="S87" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="88" spans="19:19">
       <c r="S88" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="89" spans="19:19">
       <c r="S89" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="90" spans="19:19">
       <c r="S90" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="91" spans="19:19">
       <c r="S91" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="92" spans="19:19">
       <c r="S92" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="93" spans="19:19">
       <c r="S93" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="94" spans="19:19">
       <c r="S94" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="95" spans="19:19">
       <c r="S95" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="96" spans="19:19">
       <c r="S96" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="97" spans="19:19">
       <c r="S97" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="98" spans="19:19">
       <c r="S98" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="99" spans="19:19">
       <c r="S99" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="100" spans="19:19">
       <c r="S100" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="101" spans="19:19">
       <c r="S101" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="102" spans="19:19">
       <c r="S102" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="103" spans="19:19">
       <c r="S103" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="104" spans="19:19">
       <c r="S104" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="105" spans="19:19">
       <c r="S105" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="106" spans="19:19">
       <c r="S106" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="107" spans="19:19">
       <c r="S107" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="108" spans="19:19">
       <c r="S108" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="109" spans="19:19">
       <c r="S109" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="110" spans="19:19">
       <c r="S110" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="111" spans="19:19">
       <c r="S111" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="112" spans="19:19">
       <c r="S112" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="113" spans="19:19">
       <c r="S113" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="114" spans="19:19">
       <c r="S114" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="115" spans="19:19">
       <c r="S115" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="116" spans="19:19">
       <c r="S116" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="117" spans="19:19">
       <c r="S117" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="118" spans="19:19">
       <c r="S118" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="119" spans="19:19">
       <c r="S119" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="120" spans="19:19">
       <c r="S120" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="121" spans="19:19">
       <c r="S121" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="122" spans="19:19">
       <c r="S122" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="123" spans="19:19">
       <c r="S123" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="124" spans="19:19">
       <c r="S124" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="125" spans="19:19">
       <c r="S125" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="126" spans="19:19">
       <c r="S126" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="127" spans="19:19">
       <c r="S127" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="128" spans="19:19">
       <c r="S128" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="129" spans="19:19">
       <c r="S129" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="130" spans="19:19">
       <c r="S130" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="131" spans="19:19">
       <c r="S131" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="132" spans="19:19">
       <c r="S132" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="133" spans="19:19">
       <c r="S133" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="134" spans="19:19">
       <c r="S134" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="135" spans="19:19">
       <c r="S135" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="136" spans="19:19">
       <c r="S136" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="137" spans="19:19">
       <c r="S137" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="138" spans="19:19">
       <c r="S138" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="139" spans="19:19">
       <c r="S139" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="140" spans="19:19">
       <c r="S140" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="141" spans="19:19">
       <c r="S141" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="142" spans="19:19">
       <c r="S142" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="143" spans="19:19">
       <c r="S143" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="144" spans="19:19">
       <c r="S144" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="145" spans="19:19">
       <c r="S145" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="146" spans="19:19">
       <c r="S146" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="147" spans="19:19">
       <c r="S147" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="148" spans="19:19">
       <c r="S148" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="149" spans="19:19">
       <c r="S149" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="150" spans="19:19">
       <c r="S150" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="151" spans="19:19">
       <c r="S151" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="152" spans="19:19">
       <c r="S152" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="153" spans="19:19">
       <c r="S153" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="154" spans="19:19">
       <c r="S154" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="155" spans="19:19">
       <c r="S155" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="156" spans="19:19">
       <c r="S156" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="157" spans="19:19">
       <c r="S157" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="158" spans="19:19">
       <c r="S158" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="159" spans="19:19">
       <c r="S159" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="160" spans="19:19">
       <c r="S160" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="161" spans="19:19">
       <c r="S161" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="162" spans="19:19">
       <c r="S162" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="163" spans="19:19">
       <c r="S163" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="164" spans="19:19">
       <c r="S164" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="165" spans="19:19">
       <c r="S165" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="166" spans="19:19">
       <c r="S166" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="167" spans="19:19">
       <c r="S167" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="168" spans="19:19">
       <c r="S168" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="169" spans="19:19">
       <c r="S169" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="170" spans="19:19">
       <c r="S170" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="171" spans="19:19">
       <c r="S171" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="172" spans="19:19">
       <c r="S172" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="173" spans="19:19">
       <c r="S173" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="174" spans="19:19">
       <c r="S174" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="175" spans="19:19">
       <c r="S175" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="176" spans="19:19">
       <c r="S176" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="177" spans="19:19">
       <c r="S177" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="178" spans="19:19">
       <c r="S178" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="179" spans="19:19">
       <c r="S179" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="180" spans="19:19">
       <c r="S180" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="181" spans="19:19">
       <c r="S181" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="182" spans="19:19">
       <c r="S182" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="183" spans="19:19">
       <c r="S183" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="184" spans="19:19">
       <c r="S184" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="185" spans="19:19">
       <c r="S185" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="186" spans="19:19">
       <c r="S186" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="187" spans="19:19">
       <c r="S187" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="188" spans="19:19">
       <c r="S188" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="189" spans="19:19">
       <c r="S189" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="190" spans="19:19">
       <c r="S190" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="191" spans="19:19">
       <c r="S191" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="192" spans="19:19">
       <c r="S192" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="193" spans="19:19">
       <c r="S193" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="194" spans="19:19">
       <c r="S194" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="195" spans="19:19">
       <c r="S195" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="196" spans="19:19">
       <c r="S196" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="197" spans="19:19">
       <c r="S197" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="198" spans="19:19">
       <c r="S198" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="199" spans="19:19">
       <c r="S199" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="200" spans="19:19">
       <c r="S200" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="201" spans="19:19">
       <c r="S201" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="202" spans="19:19">
       <c r="S202" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="203" spans="19:19">
       <c r="S203" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="204" spans="19:19">
       <c r="S204" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="205" spans="19:19">
       <c r="S205" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="206" spans="19:19">
       <c r="S206" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="207" spans="19:19">
       <c r="S207" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="208" spans="19:19">
       <c r="S208" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="209" spans="19:19">
       <c r="S209" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="210" spans="19:19">
       <c r="S210" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="211" spans="19:19">
       <c r="S211" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="212" spans="19:19">
       <c r="S212" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="213" spans="19:19">
       <c r="S213" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="214" spans="19:19">
       <c r="S214" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="215" spans="19:19">
       <c r="S215" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="216" spans="19:19">
       <c r="S216" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="217" spans="19:19">
       <c r="S217" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="218" spans="19:19">
       <c r="S218" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="219" spans="19:19">
       <c r="S219" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="220" spans="19:19">
       <c r="S220" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="221" spans="19:19">
       <c r="S221" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="222" spans="19:19">
       <c r="S222" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="223" spans="19:19">
       <c r="S223" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="224" spans="19:19">
       <c r="S224" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="225" spans="19:19">
       <c r="S225" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="226" spans="19:19">
       <c r="S226" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="227" spans="19:19">
       <c r="S227" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="228" spans="19:19">
       <c r="S228" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="229" spans="19:19">
       <c r="S229" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="230" spans="19:19">
       <c r="S230" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="231" spans="19:19">
       <c r="S231" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="232" spans="19:19">
       <c r="S232" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="233" spans="19:19">
       <c r="S233" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="234" spans="19:19">
       <c r="S234" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="235" spans="19:19">
       <c r="S235" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="236" spans="19:19">
       <c r="S236" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="237" spans="19:19">
       <c r="S237" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="238" spans="19:19">
       <c r="S238" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="239" spans="19:19">
       <c r="S239" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="240" spans="19:19">
       <c r="S240" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="241" spans="19:19">
       <c r="S241" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="242" spans="19:19">
       <c r="S242" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="243" spans="19:19">
       <c r="S243" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="244" spans="19:19">
       <c r="S244" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="245" spans="19:19">
       <c r="S245" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="246" spans="19:19">
       <c r="S246" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="247" spans="19:19">
       <c r="S247" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="248" spans="19:19">
       <c r="S248" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="249" spans="19:19">
       <c r="S249" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="250" spans="19:19">
       <c r="S250" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="251" spans="19:19">
       <c r="S251" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="252" spans="19:19">
       <c r="S252" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="253" spans="19:19">
       <c r="S253" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="254" spans="19:19">
       <c r="S254" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="255" spans="19:19">
       <c r="S255" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="256" spans="19:19">
       <c r="S256" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="257" spans="19:19">
       <c r="S257" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="258" spans="19:19">
       <c r="S258" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="259" spans="19:19">
       <c r="S259" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="260" spans="19:19">
       <c r="S260" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="261" spans="19:19">
       <c r="S261" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="262" spans="19:19">
       <c r="S262" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="263" spans="19:19">
       <c r="S263" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="264" spans="19:19">
       <c r="S264" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="265" spans="19:19">
       <c r="S265" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="266" spans="19:19">
       <c r="S266" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="267" spans="19:19">
       <c r="S267" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="268" spans="19:19">
       <c r="S268" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="269" spans="19:19">
       <c r="S269" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="270" spans="19:19">
       <c r="S270" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="271" spans="19:19">
       <c r="S271" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="272" spans="19:19">
       <c r="S272" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="273" spans="19:19">
       <c r="S273" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="274" spans="19:19">
       <c r="S274" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="275" spans="19:19">
       <c r="S275" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="276" spans="19:19">
       <c r="S276" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="277" spans="19:19">
       <c r="S277" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="278" spans="19:19">
       <c r="S278" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="279" spans="19:19">
       <c r="S279" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="280" spans="19:19">
       <c r="S280" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="281" spans="19:19">
       <c r="S281" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="282" spans="19:19">
       <c r="S282" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="283" spans="19:19">
       <c r="S283" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="284" spans="19:19">
       <c r="S284" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="285" spans="19:19">
       <c r="S285" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="286" spans="19:19">
       <c r="S286" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="287" spans="19:19">
       <c r="S287" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="288" spans="19:19">
       <c r="S288" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="289" spans="19:19">
       <c r="S289" t="s">
-        <v>585</v>
+        <v>586</v>
+      </c>
+    </row>
+    <row r="290" spans="19:19">
+      <c r="S290" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="291" spans="19:19">
+      <c r="S291" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="292" spans="19:19">
+      <c r="S292" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="293" spans="19:19">
+      <c r="S293" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="294" spans="19:19">
+      <c r="S294" t="s">
+        <v>591</v>
       </c>
     </row>
   </sheetData>

--- a/templates/ERC000041/metadata_template_ERC000041.xlsx
+++ b/templates/ERC000041/metadata_template_ERC000041.xlsx
@@ -930,7 +930,7 @@
     <t>amount or size of sample collected</t>
   </si>
   <si>
-    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: m3)</t>
+    <t>(Optional) The total amount or size (volume (ml), mass (g) or area (m2) ) of sample collected. (Units: kg)</t>
   </si>
   <si>
     <t>sampling time point</t>
